--- a/results/exp05-c100-resnet-bw10-40-fedavg-old-drop25/20260924-070058/rounds.xlsx
+++ b/results/exp05-c100-resnet-bw10-40-fedavg-old-drop25/20260924-070058/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2776,6 +2776,6065 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:28:45</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.119473016866827</v>
+      </c>
+      <c r="F29" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="G29" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" t="n">
+        <v>60.0769</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1:00.08</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>58.6358</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.2656</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1666.843</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>27:46.84</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>6,9,0,8,2,5,1,3,4,7</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>6:16;9:27;0:26;8:16;2:10;5:18;1:14;3:10;4:10;7:10</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>6:[];9:[4,7];0:[4,6];8:[6];2:[];5:[7];1:[];3:[5];4:[];7:[]</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>c6:bw=16,experts=[]; c9:bw=27,experts=[4,7]; c0:bw=26,experts=[4,6]; c8:bw=16,experts=[6]; c2:bw=10,experts=[]; c5:bw=18,experts=[7]; c1:bw=14,experts=[]; c3:bw=10,experts=[5]; c4:bw=10,experts=[]; c7:bw=10,experts=[]</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>8.0352,3.9711,5.3792,5.9862,4.3039,7.1708,4.9291,5.9362,7.6545,5.2696</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:29:46</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.127833249080604</v>
+      </c>
+      <c r="F30" t="n">
+        <v>39.38</v>
+      </c>
+      <c r="G30" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="H30" t="n">
+        <v>25</v>
+      </c>
+      <c r="I30" t="n">
+        <v>60.5931</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1:00.59</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>59.1481</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.2779</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1727.4571</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>28:47.46</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>4,0,1,9,6,8,7,3,2,5</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>4:21;0:24;1:18;9:24;6:24;8:19;7:12;3:18;2:10;5:19</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4:[0];0:[4,6];1:[3];9:[4];6:[4,5];8:[4];7:[];3:[7];2:[3];5:[2]</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>c4:bw=21,experts=[0]; c0:bw=24,experts=[4,6]; c1:bw=18,experts=[3]; c9:bw=24,experts=[4]; c6:bw=24,experts=[4,5]; c8:bw=19,experts=[4]; c7:bw=12,experts=[]; c3:bw=18,experts=[7]; c2:bw=10,experts=[3]; c5:bw=19,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>8.5132,5.3898,4.9407,3.9948,7.6781,6.1590,5.2407,5.8788,4.3475,7.0054</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:30:46</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.055921681864628</v>
+      </c>
+      <c r="F31" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="G31" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="H31" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" t="n">
+        <v>60.0783</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1:00.08</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>58.6498</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.2602</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1787.5555</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>29:47.56</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5,1,9,4,0,8,6,7,3,2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>5:34;1:20;9:30;4:29;0:10;8:23;6:10;7:10;3:33;2:15</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>5:[4,5,6];1:[5];9:[2,4];4:[4];0:[0];8:[4,6];6:[0];7:[7];3:[0,2,4];2:[5]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>c5:bw=34,experts=[4,5,6]; c1:bw=20,experts=[5]; c9:bw=30,experts=[2,4]; c4:bw=29,experts=[4]; c0:bw=10,experts=[0]; c8:bw=23,experts=[4,6]; c6:bw=10,experts=[0]; c7:bw=10,experts=[7]; c3:bw=33,experts=[0,2,4]; c2:bw=15,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>7.2403,4.9742,4.0822,7.6877,5.3466,6.1612,7.6831,5.2690,5.9043,4.3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:31:46</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.977179926169597</v>
+      </c>
+      <c r="F32" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="G32" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="H32" t="n">
+        <v>31</v>
+      </c>
+      <c r="I32" t="n">
+        <v>60.0369</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1:00.04</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>58.5649</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.311</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1847.8222</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>30:47.82</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>6,4,9,1,5,8,3,2,0,7</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>6:16;4:11;9:25;1:17;5:34;8:18;3:13;2:10;0:26;7:35</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6:[4];4:[];9:[6];1:[7];5:[0,4];8:[2];3:[4];2:[];0:[4,6];7:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>c6:bw=16,experts=[4]; c4:bw=11,experts=[]; c9:bw=25,experts=[6]; c1:bw=17,experts=[7]; c5:bw=34,experts=[0,4]; c8:bw=18,experts=[2]; c3:bw=13,experts=[4]; c2:bw=10,experts=[]; c0:bw=26,experts=[4,6]; c7:bw=35,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>7.8501,7.7269,3.9970,4.9163,7.1847,6.0726,5.8951,4.2772,5.3552,5.2899</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:32:47</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.026115038922704</v>
+      </c>
+      <c r="F33" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="G33" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="H33" t="n">
+        <v>31</v>
+      </c>
+      <c r="I33" t="n">
+        <v>60.6092</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1:00.61</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>59.1245</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.3027</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1908.4507</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>31:48.45</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8,5,4,7,0,1,3,6,2,9</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>8:12;5:20;4:27;7:26;0:25;1:12;3:16;6:15;2:30;9:17</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8:[0];5:[4,6];4:[5];7:[1,4];0:[1,4];1:[0];3:[1];6:[1];2:[0,6,7];9:[0]</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>c8:bw=12,experts=[0]; c5:bw=20,experts=[4,6]; c4:bw=27,experts=[5]; c7:bw=26,experts=[1,4]; c0:bw=25,experts=[1,4]; c1:bw=12,experts=[0]; c3:bw=16,experts=[1]; c6:bw=15,experts=[1]; c2:bw=30,experts=[0,6,7]; c9:bw=17,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>6.1300,7.1702,7.8073,5.3054,5.4849,5.0315,5.9447,7.7846,4.4441,4.0218</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:33:48</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.977707541546261</v>
+      </c>
+      <c r="F34" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="G34" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="H34" t="n">
+        <v>33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>61.0932</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1:01.09</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>59.6593</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.2757</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1969.5682</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>32:49.57</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7,1,3,6,5,9,2,8,4,0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>7:29;1:19;3:39;6:20;5:16;9:23;2:13;8:28;4:25;0:35</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>7:[3];1:[4];3:[4,6];6:[3,4];5:[1];9:[1,4];2:[];8:[1,3];4:[1,6];0:[3,4,6]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>c7:bw=29,experts=[3]; c1:bw=19,experts=[4]; c3:bw=39,experts=[4,6]; c6:bw=20,experts=[3,4]; c5:bw=16,experts=[1]; c9:bw=23,experts=[1,4]; c2:bw=13,experts=[]; c8:bw=28,experts=[1,3]; c4:bw=25,experts=[1,6]; c0:bw=35,experts=[3,4,6]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>5.4658,5.0470,5.7170,7.7629,7.3371,4.2809,4.6521,6.4600,8.0329,4.9036</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:34:48</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.915433171715364</v>
+      </c>
+      <c r="F35" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="G35" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="H35" t="n">
+        <v>33</v>
+      </c>
+      <c r="I35" t="n">
+        <v>59.9298</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0:59.93</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>58.3959</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2029.5182</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>33:49.52</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4,1,6,9,8,0,5,7,3,2</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4:26;1:26;6:27;9:38;8:23;0:12;5:33;7:18;3:40;2:30</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4:[3,7];1:[1,4];6:[2];9:[3,4,6];8:[4,7];0:[];5:[3,4];7:[2];3:[0,3,4,6];2:[1,2,4]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>c4:bw=26,experts=[3,7]; c1:bw=26,experts=[1,4]; c6:bw=27,experts=[2]; c9:bw=38,experts=[3,4,6]; c8:bw=23,experts=[4,7]; c0:bw=12,experts=[]; c5:bw=33,experts=[3,4]; c7:bw=18,experts=[2]; c3:bw=40,experts=[0,3,4,6]; c2:bw=30,experts=[1,2,4]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>7.3017,4.6813,7.4169,4.2910,6.1935,5.4812,7.2769,5.3059,6.0408,4.4065</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:35:49</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.955889131446851</v>
+      </c>
+      <c r="F36" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="G36" t="n">
+        <v>46.22</v>
+      </c>
+      <c r="H36" t="n">
+        <v>33</v>
+      </c>
+      <c r="I36" t="n">
+        <v>60.9863</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1:00.99</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>59.4534</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.3623</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2090.5266</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>34:50.53</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>4,0,1,6,2,8,9,7,5,3</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>4:18;0:11;1:17;6:24;2:25;8:28;9:15;7:27;5:23;3:13</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>4:[2];0:[2];1:[2];6:[6,7];2:[4,6];8:[4,5];9:[5];7:[5];5:[4,6];3:[]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>c4:bw=18,experts=[2]; c0:bw=11,experts=[2]; c1:bw=17,experts=[2]; c6:bw=24,experts=[6,7]; c2:bw=25,experts=[4,6]; c8:bw=28,experts=[4,5]; c9:bw=15,experts=[5]; c7:bw=27,experts=[5]; c5:bw=23,experts=[4,6]; c3:bw=13,experts=[]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>7.9030,5.3667,4.9798,7.9013,4.4847,6.1718,4.0541,5.3940,7.2033,5.9947</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:36:50</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.87249019525607</v>
+      </c>
+      <c r="F37" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="G37" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="H37" t="n">
+        <v>36</v>
+      </c>
+      <c r="I37" t="n">
+        <v>60.894</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1:00.89</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>59.3996</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2151.4467</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>35:51.45</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>9,0,3,7,6,5,1,4,8,2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>9:21;0:20;3:33;7:15;6:24;5:27;1:10;4:40;8:28;2:28</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9:[4,7];0:[5,7];3:[4,5,6];7:[4];6:[4,6];5:[4,7];1:[];4:[0,4,5,6];8:[4];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>c9:bw=21,experts=[4,7]; c0:bw=20,experts=[5,7]; c3:bw=33,experts=[4,5,6]; c7:bw=15,experts=[4]; c6:bw=24,experts=[4,6]; c5:bw=27,experts=[4,7]; c1:bw=10,experts=[]; c4:bw=40,experts=[0,4,5,6]; c8:bw=28,experts=[4]; c2:bw=28,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>4.0761,5.4221,5.9620,5.3528,7.8905,7.3095,5.0056,7.8623,6.0909,4.4276</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:37:51</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.831115563704195</v>
+      </c>
+      <c r="F38" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="G38" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37</v>
+      </c>
+      <c r="I38" t="n">
+        <v>61.0025</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1:01.00</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>59.5516</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.2979</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2212.4748</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>36:52.47</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1,5,2,6,4,7,9,0,3,8</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1:10;5:22;2:20;6:36;4:22;7:23;9:22;0:30;3:20;8:10</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1:[6];5:[2,4];2:[3,4];6:[4,5];4:[4,6];7:[4,6];9:[4,6];0:[4,6];3:[4,7];8:[4]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[6]; c5:bw=22,experts=[2,4]; c2:bw=20,experts=[3,4]; c6:bw=36,experts=[4,5]; c4:bw=22,experts=[4,6]; c7:bw=23,experts=[4,6]; c9:bw=22,experts=[4,6]; c0:bw=30,experts=[4,6]; c3:bw=20,experts=[4,7]; c8:bw=10,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>5.0058,7.2782,4.3775,7.8459,8.0062,5.3204,4.1135,5.4004,5.9485,6.2551</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:38:52</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.870176901795226</v>
+      </c>
+      <c r="F39" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="G39" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="H39" t="n">
+        <v>37</v>
+      </c>
+      <c r="I39" t="n">
+        <v>60.8128</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1:00.81</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>59.3568</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.2828</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2273.5172</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>37:53.52</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>8,6,4,1,5,2,3,7,9,0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>8:25;6:10;4:29;1:17;5:10;2:10;3:21;7:28;9:14;0:22</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>8:[4,6];6:[0];4:[4,6];1:[3];5:[];2:[5];3:[2,4];7:[4,7];9:[2];0:[0,4]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>c8:bw=25,experts=[4,6]; c6:bw=10,experts=[0]; c4:bw=29,experts=[4,6]; c1:bw=17,experts=[3]; c5:bw=10,experts=[]; c2:bw=10,experts=[5]; c3:bw=21,experts=[2,4]; c7:bw=28,experts=[4,7]; c9:bw=14,experts=[2]; c0:bw=22,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>6.1760,7.7808,7.7623,4.9989,7.1964,4.4145,6.0770,5.3455,4.0412,5.5643</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:39:53</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.836767785019783</v>
+      </c>
+      <c r="F40" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="G40" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="H40" t="n">
+        <v>37</v>
+      </c>
+      <c r="I40" t="n">
+        <v>60.5446</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1:00.54</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>59.0535</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2334.0911</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>38:54.09</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3,0,1,7,6,8,2,4,9,5</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>3:14;0:10;1:25;7:22;6:17;8:25;2:20;4:20;9:13;5:40</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3:[4];0:[4];1:[5,7];7:[0];6:[];8:[2,4];2:[4];4:[4,6];9:[4];5:[0,4,5,6]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>c3:bw=14,experts=[4]; c0:bw=10,experts=[4]; c1:bw=25,experts=[5,7]; c7:bw=22,experts=[0]; c6:bw=17,experts=[]; c8:bw=25,experts=[2,4]; c2:bw=20,experts=[4]; c4:bw=20,experts=[4,6]; c9:bw=13,experts=[4]; c5:bw=40,experts=[0,4,5,6]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>6.0118,5.4637,4.9606,5.3122,7.7604,6.0627,4.3455,7.7517,4.0511,7.3336</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:40:53</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.815515428579352</v>
+      </c>
+      <c r="F41" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="G41" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="H41" t="n">
+        <v>37</v>
+      </c>
+      <c r="I41" t="n">
+        <v>60.4854</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1:00.49</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>59.0367</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.2894</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2394.5977</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>39:54.60</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8,1,5,6,2,7,3,4,9,0</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8:14;1:23;5:18;6:26;2:36;7:37;3:10;4:11;9:22;0:20</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8:[0];1:[0];5:[4];6:[1,4];2:[0,4,7];7:[1,4,6];3:[1];4:[];9:[0,4];0:[1,4]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>c8:bw=14,experts=[0]; c1:bw=23,experts=[0]; c5:bw=18,experts=[4]; c6:bw=26,experts=[1,4]; c2:bw=36,experts=[0,4,7]; c7:bw=37,experts=[1,4,6]; c3:bw=10,experts=[1]; c4:bw=11,experts=[]; c9:bw=22,experts=[0,4]; c0:bw=20,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>6.1465,5.0486,7.3203,7.8493,4.4007,5.2653,5.9590,7.6589,3.7419,5.6460</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:41:54</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.773618824925724</v>
+      </c>
+      <c r="F42" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="G42" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="H42" t="n">
+        <v>41</v>
+      </c>
+      <c r="I42" t="n">
+        <v>60.7274</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1:00.73</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>59.2402</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.1855</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.3003</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2455.3514</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>40:55.35</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2,6,8,1,4,5,7,3,9,0</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2:30;6:10;8:31;1:10;4:28;5:34;7:38;3:22;9:30;0:10</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2:[4,6];6:[3];8:[1,3,4];1:[4];4:[1,4];5:[1,4,6];7:[3,4,6];3:[4];9:[1,4,6];0:[3]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>c2:bw=30,experts=[4,6]; c6:bw=10,experts=[3]; c8:bw=31,experts=[1,3,4]; c1:bw=10,experts=[4]; c4:bw=28,experts=[1,4]; c5:bw=34,experts=[1,4,6]; c7:bw=38,experts=[3,4,6]; c3:bw=22,experts=[4]; c9:bw=30,experts=[1,4,6]; c0:bw=10,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4.4231,8.1716,6.6578,5.2751,7.8711,6.8676,4.9428,5.6368,3.8104,5.5839</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:42:55</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.810781957598375</v>
+      </c>
+      <c r="F43" t="n">
+        <v>50.24</v>
+      </c>
+      <c r="G43" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="H43" t="n">
+        <v>41</v>
+      </c>
+      <c r="I43" t="n">
+        <v>61.0255</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1:01.03</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>59.5151</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.1813</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.3214</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2516.4027</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>41:56.40</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5,1,3,9,6,0,7,4,8,2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5:28;1:27;3:27;9:28;6:19;0:10;7:11;4:30;8:23;2:22</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5:[3];1:[1,4];3:[0,3];9:[3,4];6:[2];0:[4];7:[2];4:[3,4,7];8:[4,7];2:[1,2]</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>c5:bw=28,experts=[3]; c1:bw=27,experts=[1,4]; c3:bw=27,experts=[0,3]; c9:bw=28,experts=[3,4]; c6:bw=19,experts=[2]; c0:bw=10,experts=[4]; c7:bw=11,experts=[2]; c4:bw=30,experts=[3,4,7]; c8:bw=23,experts=[4,7]; c2:bw=22,experts=[1,2]</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>7.2580,5.0385,6.0284,4.1016,7.9047,5.4201,5.3643,7.8000,6.2341,4.3653</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:43:56</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.808514476835697</v>
+      </c>
+      <c r="F44" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="G44" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="H44" t="n">
+        <v>41</v>
+      </c>
+      <c r="I44" t="n">
+        <v>61.0415</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1:01.04</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>59.5465</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.3265</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2577.4704</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>42:57.47</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5,1,2,8,9,7,4,6,3,0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5:29;1:32;2:28;8:25;9:18;7:12;4:19;6:10;3:36;0:12</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5:[4,6];1:[2,4,6];2:[4,6];8:[4,5];9:[5];7:[5];4:[2];6:[7];3:[4,6];0:[2]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>c5:bw=29,experts=[4,6]; c1:bw=32,experts=[2,4,6]; c2:bw=28,experts=[4,6]; c8:bw=25,experts=[4,5]; c9:bw=18,experts=[5]; c7:bw=12,experts=[5]; c4:bw=19,experts=[2]; c6:bw=10,experts=[7]; c3:bw=36,experts=[4,6]; c0:bw=12,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>7.3193,5.0693,4.3779,6.1586,4.1389,5.2971,7.8206,7.8686,6.1076,5.3887</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:44:57</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.775496740244563</v>
+      </c>
+      <c r="F45" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="G45" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="H45" t="n">
+        <v>44</v>
+      </c>
+      <c r="I45" t="n">
+        <v>61.0994</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1:01.10</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>59.6509</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.2966</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2638.5935</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>43:58.59</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0,3,4,2,7,5,6,9,8,1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0:37;3:26;4:16;2:20;7:40;5:13;6:11;9:21;8:19;1:25</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0:[4,5,7];3:[4,5];4:[0];2:[4,6];7:[0,4,5,6];5:[7];6:[6];9:[7];8:[4];1:[4,6]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>c0:bw=37,experts=[4,5,7]; c3:bw=26,experts=[4,5]; c4:bw=16,experts=[0]; c2:bw=20,experts=[4,6]; c7:bw=40,experts=[0,4,5,6]; c5:bw=13,experts=[7]; c6:bw=11,experts=[6]; c9:bw=21,experts=[7]; c8:bw=19,experts=[4]; c1:bw=25,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>5.4388,6.0197,7.8438,4.5348,5.3056,7.2907,7.8555,4.0157,6.2852,5.0610</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:45:58</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.747480825576079</v>
+      </c>
+      <c r="F46" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="G46" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="H46" t="n">
+        <v>45</v>
+      </c>
+      <c r="I46" t="n">
+        <v>61.1545</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1:01.15</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>59.6692</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.3278</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2699.7704</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>44:59.77</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8,0,3,4,7,2,9,6,5,1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8:31;0:20;3:37;4:36;7:20;2:27;9:14;6:10;5:25;1:31</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8:[4,6];0:[4,6];3:[4,6,7];4:[4,5,6];7:[4];2:[3,4];9:[4];6:[5];5:[2];1:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>c8:bw=31,experts=[4,6]; c0:bw=20,experts=[4,6]; c3:bw=37,experts=[4,6,7]; c4:bw=36,experts=[4,5,6]; c7:bw=20,experts=[4]; c2:bw=27,experts=[3,4]; c9:bw=14,experts=[4]; c6:bw=10,experts=[5]; c5:bw=25,experts=[2]; c1:bw=31,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6.1754,5.4878,6.0380,8.0036,5.2934,4.4017,4.0450,7.8252,7.3355,5.0635</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:46:59</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.748365206679596</v>
+      </c>
+      <c r="F47" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="H47" t="n">
+        <v>45</v>
+      </c>
+      <c r="I47" t="n">
+        <v>61.2289</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1:01.23</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>59.7616</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2761.0231</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>46:01.02</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9,3,6,1,4,5,2,8,0,7</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>9:20;3:15;6:21;1:23;4:35;5:23;2:32;8:22;0:30;7:16</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>9:[2,4];3:[2];6:[0];1:[3,4];4:[4,5,6];5:[4,6];2:[4,5,6];8:[4,6];0:[0,4,6];7:[7]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>c9:bw=20,experts=[2,4]; c3:bw=15,experts=[2]; c6:bw=21,experts=[0]; c1:bw=23,experts=[3,4]; c4:bw=35,experts=[4,5,6]; c5:bw=23,experts=[4,6]; c2:bw=32,experts=[4,5,6]; c8:bw=22,experts=[4,6]; c0:bw=30,experts=[0,4,6]; c7:bw=16,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>4.1261,6.0182,7.8797,5.1269,7.8859,7.2786,4.3831,6.1588,5.5724,5.3317</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:48:01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.71546793717019</v>
+      </c>
+      <c r="F48" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="G48" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="H48" t="n">
+        <v>47</v>
+      </c>
+      <c r="I48" t="n">
+        <v>61.091</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1:01.09</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>59.6238</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.2868</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2822.1374</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>47:02.14</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5,6,7,9,8,3,4,0,1,2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>5:29;6:12;7:29;9:10;8:22;3:39;4:10;0:25;1:17;2:30</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>5:[0,5];6:[4];7:[4,6];9:[];8:[2,4];3:[0,4,6];4:[4];0:[4];1:[];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>c5:bw=29,experts=[0,5]; c6:bw=12,experts=[4]; c7:bw=29,experts=[4,6]; c9:bw=10,experts=[]; c8:bw=22,experts=[2,4]; c3:bw=39,experts=[0,4,6]; c4:bw=10,experts=[4]; c0:bw=25,experts=[4]; c1:bw=17,experts=[]; c2:bw=30,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>7.3242,7.8555,5.4548,4.0488,6.1741,5.9613,7.8107,5.5559,5.0216,4.4168</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:49:03</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.740865511846089</v>
+      </c>
+      <c r="F49" t="n">
+        <v>53.54</v>
+      </c>
+      <c r="G49" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="H49" t="n">
+        <v>47</v>
+      </c>
+      <c r="I49" t="n">
+        <v>62.2144</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1:02.21</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>60.6461</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.3975</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2884.3811</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>48:04.38</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1,8,4,2,9,6,5,7,0,3</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1:28;8:28;4:37;2:31;9:29;6:25;5:31;7:35;0:10;3:10</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1:[0,7];8:[0,4];4:[4,5,6];2:[0,7];9:[0,4];6:[1];5:[4,5,6];7:[1,4,6];0:[];3:[]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>c1:bw=28,experts=[0,7]; c8:bw=28,experts=[0,4]; c4:bw=37,experts=[4,5,6]; c2:bw=31,experts=[0,7]; c9:bw=29,experts=[0,4]; c6:bw=25,experts=[1]; c5:bw=31,experts=[4,5,6]; c7:bw=35,experts=[1,4,6]; c0:bw=10,experts=[]; c3:bw=10,experts=[]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>5.0574,6.2522,8.0675,4.3300,3.7800,8.0053,7.5060,5.7486,5.6303,6.2686</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:50:02</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.74024306282546</v>
+      </c>
+      <c r="F50" t="n">
+        <v>51.81</v>
+      </c>
+      <c r="G50" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="H50" t="n">
+        <v>47</v>
+      </c>
+      <c r="I50" t="n">
+        <v>59.2546</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0:59.25</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>57.7767</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.3114</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2943.6618</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>49:03.66</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4,3,8,0,2,5,6,7,9,1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>4:27;3:18;8:15;0:11;2:32;5:31;6:10;7:24;9:29;1:30</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4:[1];3:[1];8:[1];0:[1];2:[4,5,6];5:[1,4];6:[];7:[3,4];9:[1,6];1:[4,6]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>c4:bw=27,experts=[1]; c3:bw=18,experts=[1]; c8:bw=15,experts=[1]; c0:bw=11,experts=[1]; c2:bw=32,experts=[4,5,6]; c5:bw=31,experts=[1,4]; c6:bw=10,experts=[]; c7:bw=24,experts=[3,4]; c9:bw=29,experts=[1,6]; c1:bw=30,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>7.2473,5.6807,5.7374,5.0641,4.1072,7.5877,7.7829,5.4538,4.0769,5.0387</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:51:03</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.739348424657929</v>
+      </c>
+      <c r="F51" t="n">
+        <v>53.36</v>
+      </c>
+      <c r="G51" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="H51" t="n">
+        <v>47</v>
+      </c>
+      <c r="I51" t="n">
+        <v>60.5715</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1:00.57</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>59.1331</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3004.2572</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>50:04.26</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>8,4,7,6,2,1,3,0,9,5</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>8:18;4:10;7:19;6:38;2:35;1:36;3:22;0:16;9:15;5:17</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8:[3];4:[3];7:[2];6:[2,3,4];2:[1,2,4];1:[1,4];3:[3,4];0:[3];9:[];5:[3]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>c8:bw=18,experts=[3]; c4:bw=10,experts=[3]; c7:bw=19,experts=[2]; c6:bw=38,experts=[2,3,4]; c2:bw=35,experts=[1,2,4]; c1:bw=36,experts=[1,4]; c3:bw=22,experts=[3,4]; c0:bw=16,experts=[3]; c9:bw=15,experts=[]; c5:bw=17,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>6.1595,7.7947,5.5090,7.7687,4.3889,5.0212,5.8844,5.4124,4.0287,7.1658</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:52:04</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.714734616468209</v>
+      </c>
+      <c r="F52" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="G52" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="H52" t="n">
+        <v>47</v>
+      </c>
+      <c r="I52" t="n">
+        <v>60.8453</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1:00.85</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>59.3814</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.2967</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3065.1317</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>51:05.13</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5,0,1,2,8,6,9,3,4,7</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5:26;0:30;1:12;2:11;8:26;6:29;9:10;3:31;4:10;7:15</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>5:[4,6];0:[2,4,6];1:[2];2:[4];8:[5,7];6:[7];9:[];3:[0,4,6];4:[7];7:[4]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>c5:bw=26,experts=[4,6]; c0:bw=30,experts=[2,4,6]; c1:bw=12,experts=[2]; c2:bw=11,experts=[4]; c8:bw=26,experts=[5,7]; c6:bw=29,experts=[7]; c9:bw=10,experts=[]; c3:bw=31,experts=[0,4,6]; c4:bw=10,experts=[7]; c7:bw=15,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>7.2600,5.4051,5.1203,4.3855,6.1369,7.9305,4.0263,6.0687,7.7822,5.2661</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:53:05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.73903085220546</v>
+      </c>
+      <c r="F53" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="G53" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="H53" t="n">
+        <v>47</v>
+      </c>
+      <c r="I53" t="n">
+        <v>61.4495</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1:01.45</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>59.9654</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.3167</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3126.6118</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>52:06.61</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0,8,5,7,1,4,9,6,2,3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0:26;8:10;5:13;7:19;1:22;4:18;9:17;6:28;2:16;3:24</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0:[5,7];8:[4];5:[];7:[0];1:[4,6];4:[2];9:[];6:[6];2:[4];3:[5]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>c0:bw=26,experts=[5,7]; c8:bw=10,experts=[4]; c5:bw=13,experts=[]; c7:bw=19,experts=[0]; c1:bw=22,experts=[4,6]; c4:bw=18,experts=[2]; c9:bw=17,experts=[]; c6:bw=28,experts=[6]; c2:bw=16,experts=[4]; c3:bw=24,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>5.4113,6.1079,7.3975,5.3805,5.2380,7.9399,4.0797,7.9546,4.4099,6.0460</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:54:06</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.710959048978089</v>
+      </c>
+      <c r="F54" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="G54" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="H54" t="n">
+        <v>53</v>
+      </c>
+      <c r="I54" t="n">
+        <v>60.6652</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1:00.67</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>59.1894</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3187.3031</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>53:07.30</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>8,4,5,1,3,9,6,7,0,2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8:12;4:16;5:24;1:33;3:26;9:34;6:20;7:24;0:21;2:29</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8:[];4:[0];5:[7];1:[4,5,6];3:[7];9:[3,5];6:[4,5];7:[4,5];0:[4];2:[3,4]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>c8:bw=12,experts=[]; c4:bw=16,experts=[0]; c5:bw=24,experts=[7]; c1:bw=33,experts=[4,5,6]; c3:bw=26,experts=[7]; c9:bw=34,experts=[3,5]; c6:bw=20,experts=[4,5]; c7:bw=24,experts=[4,5]; c0:bw=21,experts=[4]; c2:bw=29,experts=[3,4]</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>6.1592,7.9461,7.2340,5.0242,5.9130,4.0269,7.8834,5.3056,5.3480,4.3489</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:55:07</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.690220146845406</v>
+      </c>
+      <c r="F55" t="n">
+        <v>55.82</v>
+      </c>
+      <c r="G55" t="n">
+        <v>55.82</v>
+      </c>
+      <c r="H55" t="n">
+        <v>54</v>
+      </c>
+      <c r="I55" t="n">
+        <v>61.5565</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1:01.56</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>60.0477</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.3256</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3248.8887</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>54:08.89</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2,1,8,7,3,0,6,5,9,4</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2:10;1:29;8:31;7:34;3:17;0:20;6:30;5:10;9:28;4:18</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2:[4];1:[3,4];8:[4,5,6];7:[4,7];3:[2];0:[0,4];6:[0,4,6];5:[2];9:[2,7];4:[4]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>c2:bw=10,experts=[4]; c1:bw=29,experts=[3,4]; c8:bw=31,experts=[4,5,6]; c7:bw=34,experts=[4,7]; c3:bw=17,experts=[2]; c0:bw=20,experts=[0,4]; c6:bw=30,experts=[0,4,6]; c5:bw=10,experts=[2]; c9:bw=28,experts=[2,7]; c4:bw=18,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>4.3708,5.0535,6.3579,5.3178,5.9790,5.4171,7.8566,7.4024,4.2245,8.0680</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:56:08</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.630455978198355</v>
+      </c>
+      <c r="F56" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="G56" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="H56" t="n">
+        <v>55</v>
+      </c>
+      <c r="I56" t="n">
+        <v>60.6476</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1:00.65</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>59.2742</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.2192</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3309.5641</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>55:09.56</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7,2,4,3,8,5,1,6,0,9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>7:30;2:23;4:10;3:29;8:10;5:29;1:33;6:23;0:15;9:34</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>7:[0,4,6];2:[4,6];4:[4];3:[4,6];8:[2];5:[0,4];1:[0,4,6];6:[4];0:[4];9:[4,6]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>c7:bw=30,experts=[0,4,6]; c2:bw=23,experts=[4,6]; c4:bw=10,experts=[4]; c3:bw=29,experts=[4,6]; c8:bw=10,experts=[2]; c5:bw=29,experts=[0,4]; c1:bw=33,experts=[0,4,6]; c6:bw=23,experts=[4]; c0:bw=15,experts=[4]; c9:bw=34,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>5.3843,4.3796,7.9791,5.9588,6.0862,7.2281,5.1450,7.8430,5.3552,3.9149</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:57:08</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.68348712682421</v>
+      </c>
+      <c r="F57" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="G57" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="H57" t="n">
+        <v>55</v>
+      </c>
+      <c r="I57" t="n">
+        <v>60.2845</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1:00.28</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>58.9312</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.1919</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3369.8767</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>56:09.88</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,1,3,2,5,4,8,7,6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>9:29;1:31;3:10;2:29;5:17;4:10;8:10;7:10;6:13;0:39</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>9:[0,4];1:[4,7];3:[];2:[0,7];5:[5];4:[5];8:[0];7:[1];6:[1];0:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[0,4]; c1:bw=31,experts=[4,7]; c3:bw=10,experts=[]; c2:bw=29,experts=[0,7]; c5:bw=17,experts=[5]; c4:bw=10,experts=[5]; c8:bw=10,experts=[0]; c7:bw=10,experts=[1]; c6:bw=13,experts=[1]; c0:bw=39,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>3.7924,5.2626,6.2750,4.6491,7.5686,8.2904,5.8992,4.9263,7.1921,5.0755</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:58:03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.645387672531287</v>
+      </c>
+      <c r="F58" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="G58" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H58" t="n">
+        <v>57</v>
+      </c>
+      <c r="I58" t="n">
+        <v>54.5174</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0:54.52</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>53.2211</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.1472</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3424.4207</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>57:04.42</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3,8,6,1,7,0,5,4,2,9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3:35;8:24;6:27;1:27;7:38;0:39;5:24;4:23;2:18;9:11</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3:[1,4];8:[1,4];6:[4];1:[4,6];7:[3,4];0:[1,4,6];5:[1,4];4:[1,6];2:[5];9:[]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>c3:bw=35,experts=[1,4]; c8:bw=24,experts=[1,4]; c6:bw=27,experts=[4]; c1:bw=27,experts=[4,6]; c7:bw=38,experts=[3,4]; c0:bw=39,experts=[1,4,6]; c5:bw=24,experts=[1,4]; c4:bw=23,experts=[1,6]; c2:bw=18,experts=[5]; c9:bw=11,experts=[]</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>5.6183,5.5910,6.9906,4.4909,4.7463,4.8345,6.4641,7.0094,3.8644,3.6114</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:58:57</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.662951377413481</v>
+      </c>
+      <c r="F59" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="G59" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H59" t="n">
+        <v>57</v>
+      </c>
+      <c r="I59" t="n">
+        <v>54.1388</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0:54.14</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>52.8177</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.1694</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3478.5829</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>57:58.58</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7,2,9,6,5,1,8,4,3,0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>7:13;2:10;9:32;6:30;5:19;1:17;8:22;4:21;3:34;0:26</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>7:[2];2:[1];9:[1,4,6];6:[2,3,4];5:[3];1:[1];8:[3];4:[3,4];3:[3,4];0:[3]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>c7:bw=13,experts=[2]; c2:bw=10,experts=[1]; c9:bw=32,experts=[1,4,6]; c6:bw=30,experts=[2,3,4]; c5:bw=19,experts=[3]; c1:bw=17,experts=[1]; c8:bw=22,experts=[3]; c4:bw=21,experts=[3,4]; c3:bw=34,experts=[3,4]; c0:bw=26,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>4.7804,3.9094,3.6582,7.0096,6.4646,4.4546,5.4769,6.9624,5.3034,4.7982</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:59:51</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.613069934915344</v>
+      </c>
+      <c r="F60" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="G60" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H60" t="n">
+        <v>57</v>
+      </c>
+      <c r="I60" t="n">
+        <v>54.2986</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0:54.30</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>52.9856</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.1591</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3532.9073</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>58:52.91</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2,8,9,6,1,4,7,5,0,3</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2:20;8:31;9:15;6:11;1:36;4:14;7:15;5:18;0:29;3:20</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2:[2,4];8:[4,6,7];9:[4];6:[7];1:[2,4,6];4:[];7:[4];5:[6];0:[2,4];3:[0,4]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>c2:bw=20,experts=[2,4]; c8:bw=31,experts=[4,6,7]; c9:bw=15,experts=[4]; c6:bw=11,experts=[7]; c1:bw=36,experts=[2,4,6]; c4:bw=14,experts=[]; c7:bw=15,experts=[4]; c5:bw=18,experts=[6]; c0:bw=29,experts=[2,4]; c3:bw=20,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>3.9328,5.5149,3.6363,6.9571,4.5192,6.9741,4.7618,6.4583,4.8793,5.3517</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:00:46</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.619249481061028</v>
+      </c>
+      <c r="F61" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="G61" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="H61" t="n">
+        <v>60</v>
+      </c>
+      <c r="I61" t="n">
+        <v>54.3004</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0:54.30</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>52.9945</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.1589</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3587.2319</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>59:47.23</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0,7,4,2,5,8,6,9,1,3</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0:29;7:26;4:17;2:17;5:18;8:14;6:33;9:10;1:30;3:24</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:[4,7];7:[4];4:[7];2:[];5:[];8:[];6:[4,5,6];9:[4];1:[4,5,6];3:[4,5]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>c0:bw=29,experts=[4,7]; c7:bw=26,experts=[4]; c4:bw=17,experts=[7]; c2:bw=17,experts=[]; c5:bw=18,experts=[]; c8:bw=14,experts=[]; c6:bw=33,experts=[4,5,6]; c9:bw=10,experts=[4]; c1:bw=30,experts=[4,5,6]; c3:bw=24,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>4.8808,4.7686,7.0178,3.8955,6.4473,5.4617,7.0273,3.6476,4.5053,5.3427</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:01:40</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.624908739748424</v>
+      </c>
+      <c r="F62" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="G62" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="H62" t="n">
+        <v>60</v>
+      </c>
+      <c r="I62" t="n">
+        <v>54.5279</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0:54.53</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>53.1998</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.1763</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3641.7856</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1:00:41.79</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5,6,2,9,1,3,8,4,7,0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>5:27;6:21;2:16;9:21;1:19;3:24;8:31;4:21;7:24;0:33</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5:[4,7];6:[4,6];2:[];9:[3];1:[];3:[7];8:[4,5,6];4:[0,2];7:[4,5];0:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>c5:bw=27,experts=[4,7]; c6:bw=21,experts=[4,6]; c2:bw=16,experts=[]; c9:bw=21,experts=[3]; c1:bw=19,experts=[]; c3:bw=24,experts=[7]; c8:bw=31,experts=[4,5,6]; c4:bw=21,experts=[0,2]; c7:bw=24,experts=[4,5]; c0:bw=33,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>6.4929,7.0494,3.8979,3.6795,4.5001,5.3528,5.5300,7.0505,4.7747,4.8719</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:02:36</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.621735742624188</v>
+      </c>
+      <c r="F63" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="G63" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="H63" t="n">
+        <v>62</v>
+      </c>
+      <c r="I63" t="n">
+        <v>55.4498</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0:55.45</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>53.8328</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.4591</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3697.2606</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1:01:37.26</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>8,6,9,4,5,0,3,2,1,7</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>8:10;6:35;9:10;4:33;5:37;0:16;3:29;2:23;1:40;7:25</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>8:[];6:[0,4,6];9:[5];4:[0,4,6];5:[2,4,6];0:[0];3:[2,4];2:[3];1:[0,3,4,6];7:[4,7]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[]; c6:bw=35,experts=[0,4,6]; c9:bw=10,experts=[5]; c4:bw=33,experts=[0,4,6]; c5:bw=37,experts=[2,4,6]; c0:bw=16,experts=[0]; c3:bw=29,experts=[2,4]; c2:bw=23,experts=[3]; c1:bw=40,experts=[0,3,4,6]; c7:bw=25,experts=[4,7]</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>5.5046,7.0445,3.6410,7.0613,6.4643,4.7969,5.5990,4.0340,4.7878,4.8995</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:03:37</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.635613307636807</v>
+      </c>
+      <c r="F64" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="G64" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="H64" t="n">
+        <v>62</v>
+      </c>
+      <c r="I64" t="n">
+        <v>61.424</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1:01.42</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>59.9016</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1634</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.3509</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3758.7255</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1:02:38.73</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5,9,6,3,8,1,7,0,2,4</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>5:10;9:12;6:19;3:29;8:18;1:28;7:38;0:23;2:15;4:29</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>5:[0];9:[2];6:[4];3:[4,6];8:[2];1:[4];7:[0,6];0:[4,6];2:[6];4:[4,6]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>c5:bw=10,experts=[0]; c9:bw=12,experts=[2]; c6:bw=19,experts=[4]; c3:bw=29,experts=[4,6]; c8:bw=18,experts=[2]; c1:bw=28,experts=[4]; c7:bw=38,experts=[0,6]; c0:bw=23,experts=[4,6]; c2:bw=15,experts=[6]; c4:bw=29,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>7.4445,4.0376,7.8479,6.0139,6.2803,5.1274,5.4176,5.5873,4.3434,7.8017</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:04:39</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.598358139077345</v>
+      </c>
+      <c r="F65" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="G65" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="H65" t="n">
+        <v>64</v>
+      </c>
+      <c r="I65" t="n">
+        <v>61.6985</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1:01.70</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>60.175</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.3398</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3820.4632</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1:03:40.46</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>6,4,5,3,7,0,8,9,2,1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>6:28;4:21;5:13;3:21;7:19;0:18;8:30;9:33;2:31;1:16</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>6:[1,4];4:[4,5];5:[5];3:[4,6];7:[1];0:[4];8:[0,4,6];9:[0,4,7];2:[0,4,7];1:[]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>c6:bw=28,experts=[1,4]; c4:bw=21,experts=[4,5]; c5:bw=13,experts=[5]; c3:bw=21,experts=[4,6]; c7:bw=19,experts=[1]; c0:bw=18,experts=[4]; c8:bw=30,experts=[0,4,6]; c9:bw=33,experts=[0,4,7]; c2:bw=31,experts=[0,4,7]; c1:bw=16,experts=[]</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>7.7975,7.9629,7.1709,5.9474,5.3002,5.5372,6.4158,4.2121,4.6595,5.1715</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:05:40</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.601934762934502</v>
+      </c>
+      <c r="F66" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="G66" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="H66" t="n">
+        <v>64</v>
+      </c>
+      <c r="I66" t="n">
+        <v>61.1209</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1:01.12</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>59.6344</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1729</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.3122</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3881.62</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1:04:41.62</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7,5,4,6,8,3,0,2,1,9</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>7:10;5:16;4:32;6:28;8:37;3:24;0:23;2:16;1:32;9:26</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>7:[3];5:[1];4:[1,4];6:[4];8:[1,4,6];3:[1];0:[1,4];2:[5];1:[0,4,7];9:[4,6]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[3]; c5:bw=16,experts=[1]; c4:bw=32,experts=[1,4]; c6:bw=28,experts=[4]; c8:bw=37,experts=[1,4,6]; c3:bw=24,experts=[1]; c0:bw=23,experts=[1,4]; c2:bw=16,experts=[5]; c1:bw=32,experts=[0,4,7]; c9:bw=26,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>5.3449,7.2895,8.1467,7.8186,6.1364,5.9443,5.4902,4.3423,5.0338,4.0877</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:06:41</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.582864694627565</v>
+      </c>
+      <c r="F67" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="G67" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="H67" t="n">
+        <v>64</v>
+      </c>
+      <c r="I67" t="n">
+        <v>60.8688</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1:00.87</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>59.3615</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.3351</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3942.5276</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1:05:42.53</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2,5,1,8,9,6,4,0,3,7</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2:23;5:10;1:30;8:13;9:17;6:16;4:23;0:21;3:37;7:28</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2:[1,4];5:[3];1:[1,4,6];8:[3];9:[1];6:[];4:[3];0:[3,4];3:[3,4,6];7:[2,4]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>c2:bw=23,experts=[1,4]; c5:bw=10,experts=[3]; c1:bw=30,experts=[1,4,6]; c8:bw=13,experts=[3]; c9:bw=17,experts=[1]; c6:bw=16,experts=[]; c4:bw=23,experts=[3]; c0:bw=21,experts=[3,4]; c3:bw=37,experts=[3,4,6]; c7:bw=28,experts=[2,4]</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>4.4220,7.3658,5.0431,6.0989,4.0342,7.7217,7.8868,5.3661,5.9202,5.5027</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:07:42</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.568298410716739</v>
+      </c>
+      <c r="F68" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="G68" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="H68" t="n">
+        <v>64</v>
+      </c>
+      <c r="I68" t="n">
+        <v>61.4692</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1:01.47</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>59.9554</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.3374</v>
+      </c>
+      <c r="N68" t="n">
+        <v>4004.032</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1:06:44.03</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4,5,1,3,6,0,2,9,7,8</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:28;5:27;1:20;3:14;6:29;0:18;2:24;9:33;7:33;8:10</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>4:[4,6];5:[4,6];1:[2,4];3:[0];6:[2,3];0:[2];2:[2,4];9:[4,6];7:[1,4,6];8:[7]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>c4:bw=28,experts=[4,6]; c5:bw=27,experts=[4,6]; c1:bw=20,experts=[2,4]; c3:bw=14,experts=[0]; c6:bw=29,experts=[2,3]; c0:bw=18,experts=[2]; c2:bw=24,experts=[2,4]; c9:bw=33,experts=[4,6]; c7:bw=33,experts=[1,4,6]; c8:bw=10,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>7.9474,7.6503,5.2124,6.0055,7.7900,5.3748,4.4370,4.0800,5.3318,6.1259</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:08:45</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.573683777705768</v>
+      </c>
+      <c r="F69" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="G69" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="H69" t="n">
+        <v>64</v>
+      </c>
+      <c r="I69" t="n">
+        <v>62.0334</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1:02.03</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>60.584</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.2926</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4066.1019</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1:07:46.10</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1,8,2,0,3,4,5,9,7,6</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1:23;8:17;2:32;0:17;3:14;4:27;5:25;9:10;7:15;6:18</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1:[4,5];8:[4];2:[4,5,6];0:[7];3:[];4:[7];5:[4,6];9:[4];7:[];6:[7]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>c1:bw=23,experts=[4,5]; c8:bw=17,experts=[4]; c2:bw=32,experts=[4,5,6]; c0:bw=17,experts=[7]; c3:bw=14,experts=[]; c4:bw=27,experts=[7]; c5:bw=25,experts=[4,6]; c9:bw=10,experts=[4]; c7:bw=15,experts=[]; c6:bw=18,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>5.0284,6.2800,4.5303,5.5490,6.1428,8.0465,7.5848,4.1505,5.4706,7.8011</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:09:46</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.549267561320167</v>
+      </c>
+      <c r="F70" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="G70" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="H70" t="n">
+        <v>69</v>
+      </c>
+      <c r="I70" t="n">
+        <v>61.1528</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1:01.15</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>59.6151</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.1646</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.3718</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4127.2835</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1:08:47.28</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>3,7,1,4,9,5,0,2,8,6</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>3:23;7:32;1:17;4:23;9:20;5:22;0:29;2:37;8:23;6:15</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>3:[5];7:[4,5,6];1:[4];4:[2,4];9:[3,4];5:[4,7];0:[4,5];2:[4,5,6];8:[4,5];6:[]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>c3:bw=23,experts=[5]; c7:bw=32,experts=[4,5,6]; c1:bw=17,experts=[4]; c4:bw=23,experts=[2,4]; c9:bw=20,experts=[3,4]; c5:bw=22,experts=[4,7]; c0:bw=29,experts=[4,5]; c2:bw=37,experts=[4,5,6]; c8:bw=23,experts=[4,5]; c6:bw=15,experts=[]</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>5.9308,5.4925,5.0035,7.8418,4.1671,6.8184,5.5804,4.4300,6.2632,8.0873</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:10:46</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.581097798723051</v>
+      </c>
+      <c r="F71" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="G71" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="H71" t="n">
+        <v>69</v>
+      </c>
+      <c r="I71" t="n">
+        <v>60.3029</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1:00.30</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>58.7466</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.3879</v>
+      </c>
+      <c r="N71" t="n">
+        <v>4187.6192</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1:09:47.62</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1,9,7,3,0,6,2,4,5,8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1:13;9:10;7:16;3:18;0:17;6:14;2:31;4:32;5:13;8:27</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1:[3];9:[];7:[];3:[7];0:[0];6:[5];2:[3,4,6];4:[0,4,6];5:[2];8:[4]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>c1:bw=13,experts=[3]; c9:bw=10,experts=[]; c7:bw=16,experts=[]; c3:bw=18,experts=[7]; c0:bw=17,experts=[0]; c6:bw=14,experts=[5]; c2:bw=31,experts=[3,4,6]; c4:bw=32,experts=[0,4,6]; c5:bw=13,experts=[2]; c8:bw=27,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>5.2322,4.2645,4.8946,5.6435,4.9944,7.3615,4.2757,8.0937,7.5195,6.4670</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:11:47</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.59579460609877</v>
+      </c>
+      <c r="F72" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="G72" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="H72" t="n">
+        <v>69</v>
+      </c>
+      <c r="I72" t="n">
+        <v>61.0237</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1:01.02</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>59.5909</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.1612</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.2703</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4248.6802</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1:10:48.68</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>4,0,1,9,7,5,3,6,8,2</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>4:24;0:10;1:29;9:22;7:11;5:19;3:34;6:28;8:21;2:34</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>4:[4,6];0:[];1:[4,6];9:[2,5];7:[];5:[0];3:[2,4,6];6:[0];8:[2,4];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>c4:bw=24,experts=[4,6]; c0:bw=10,experts=[]; c1:bw=29,experts=[4,6]; c9:bw=22,experts=[2,5]; c7:bw=11,experts=[]; c5:bw=19,experts=[0]; c3:bw=34,experts=[2,4,6]; c6:bw=28,experts=[0]; c8:bw=21,experts=[2,4]; c2:bw=34,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>8.0128,5.4491,5.0606,4.1247,5.4054,7.2608,6.0333,7.7835,6.1315,4.3292</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:12:49</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.568930305100384</v>
+      </c>
+      <c r="F73" t="n">
+        <v>56.27</v>
+      </c>
+      <c r="G73" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="H73" t="n">
+        <v>69</v>
+      </c>
+      <c r="I73" t="n">
+        <v>62.0299</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1:02.03</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>60.5373</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.3238</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4310.7396</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1:11:50.74</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8,1,5,7,6,0,3,2,9,4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>8:16;1:22;5:24;7:27;6:11;0:29;3:13;2:13;9:21;4:22</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>8:[0];1:[4,6];5:[4,5];7:[0,7];6:[6];0:[4,6];3:[4];2:[];9:[0,7];4:[5]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>c8:bw=16,experts=[0]; c1:bw=22,experts=[4,6]; c5:bw=24,experts=[4,5]; c7:bw=27,experts=[0,7]; c6:bw=11,experts=[6]; c0:bw=29,experts=[4,6]; c3:bw=13,experts=[4]; c2:bw=13,experts=[]; c9:bw=21,experts=[0,7]; c4:bw=22,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>6.2502,5.2087,7.5778,5.4793,7.8270,5.6477,6.1458,4.4099,4.1282,7.8628</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:13:50</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.552786746733428</v>
+      </c>
+      <c r="F74" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="G74" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="H74" t="n">
+        <v>69</v>
+      </c>
+      <c r="I74" t="n">
+        <v>61.2933</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1:01.29</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>59.8164</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.3022</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4372.0678</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1:12:52.07</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2,8,3,1,5,9,0,7,6,4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2:26;8:10;3:22;1:37;5:10;9:29;0:16;7:20;6:11;4:23</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2:[0,7];8:[];3:[1,4];1:[0,7];5:[1];9:[4,6];0:[1];7:[3,4];6:[];4:[1,4]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>c2:bw=26,experts=[0,7]; c8:bw=10,experts=[]; c3:bw=22,experts=[1,4]; c1:bw=37,experts=[0,7]; c5:bw=10,experts=[1]; c9:bw=29,experts=[4,6]; c0:bw=16,experts=[1]; c7:bw=20,experts=[3,4]; c6:bw=11,experts=[]; c4:bw=23,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>4.5119,6.2060,6.0612,5.1155,7.2823,4.2619,5.3927,5.3645,7.7861,7.8343</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:14:52</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.551291908717387</v>
+      </c>
+      <c r="F75" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="H75" t="n">
+        <v>69</v>
+      </c>
+      <c r="I75" t="n">
+        <v>61.2205</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1:01.22</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>59.627</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.4397</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4433.3292</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1:13:53.33</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>3,0,1,5,7,8,6,2,4,9</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>3:10;0:22;1:15;5:28;7:36;8:16;6:10;2:10;4:26;9:18</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3:[3];0:[3,4];1:[1];5:[3,4];7:[2,4,6];8:[1];6:[1];2:[];4:[3];9:[]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[3]; c0:bw=22,experts=[3,4]; c1:bw=15,experts=[1]; c5:bw=28,experts=[3,4]; c7:bw=36,experts=[2,4,6]; c8:bw=16,experts=[1]; c6:bw=10,experts=[1]; c2:bw=10,experts=[]; c4:bw=26,experts=[3]; c9:bw=18,experts=[]</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>6.1465,5.4565,5.0088,7.2312,5.3417,6.2493,7.8613,4.3214,7.9111,4.0991</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:15:53</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.543754720688804</v>
+      </c>
+      <c r="F76" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="G76" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="H76" t="n">
+        <v>75</v>
+      </c>
+      <c r="I76" t="n">
+        <v>61.2753</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1:01.28</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>59.7943</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.1666</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4494.6413</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1:14:54.64</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2,9,1,3,7,6,5,4,0,8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2:22;9:34;1:30;3:11;7:16;6:31;5:17;4:31;0:34;8:30</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2:[1,2];9:[1,4];1:[2,4,6];3:[0];7:[1];6:[2,4];5:[4];4:[4,6];0:[2,4,6];8:[3,6,7]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>c2:bw=22,experts=[1,2]; c9:bw=34,experts=[1,4]; c1:bw=30,experts=[2,4,6]; c3:bw=11,experts=[0]; c7:bw=16,experts=[1]; c6:bw=31,experts=[2,4]; c5:bw=17,experts=[4]; c4:bw=31,experts=[4,6]; c0:bw=34,experts=[2,4,6]; c8:bw=30,experts=[3,6,7]</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>4.4343,4.1038,5.0550,6.0248,5.4790,7.9185,7.2268,7.7473,5.5135,6.2915</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:16:54</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.521077155814849</v>
+      </c>
+      <c r="F77" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="G77" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="H77" t="n">
+        <v>76</v>
+      </c>
+      <c r="I77" t="n">
+        <v>61.1322</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1:01.13</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>59.6808</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.2758</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4555.8046</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1:15:55.80</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8,5,0,3,2,6,7,4,9,1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>8:16;5:21;0:17;3:10;2:14;6:13;7:37;4:34;9:32;1:30</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>8:[];5:[4,6];0:[];3:[4];2:[4];6:[3];7:[4,5,6];4:[4,6,7];9:[4,5,6];1:[4,5,6]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>c8:bw=16,experts=[]; c5:bw=21,experts=[4,6]; c0:bw=17,experts=[]; c3:bw=10,experts=[4]; c2:bw=14,experts=[4]; c6:bw=13,experts=[3]; c7:bw=37,experts=[4,5,6]; c4:bw=34,experts=[4,6,7]; c9:bw=32,experts=[4,5,6]; c1:bw=30,experts=[4,5,6]</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>6.1960,7.2966,5.4153,5.9637,4.4375,7.8427,5.3909,7.8542,4.0952,5.1889</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:17:55</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.519048927039716</v>
+      </c>
+      <c r="F78" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="G78" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="H78" t="n">
+        <v>77</v>
+      </c>
+      <c r="I78" t="n">
+        <v>60.8499</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1:00.85</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>59.442</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="N78" t="n">
+        <v>4616.8951</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1:16:56.90</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9,2,1,8,4,7,6,0,3,5</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>9:16;2:19;1:35;8:10;4:10;7:10;6:32;0:35;3:22;5:33</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>9:[3];2:[5];1:[4,5,6];8:[5];4:[];7:[4];6:[4,6,7];0:[4,5,7];3:[4,5];5:[4,6,7]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>c9:bw=16,experts=[3]; c2:bw=19,experts=[5]; c1:bw=35,experts=[4,5,6]; c8:bw=10,experts=[5]; c4:bw=10,experts=[]; c7:bw=10,experts=[4]; c6:bw=32,experts=[4,6,7]; c0:bw=35,experts=[4,5,7]; c3:bw=22,experts=[4,5]; c5:bw=33,experts=[4,6,7]</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>4.1011,4.3911,4.8109,6.1353,7.9850,5.5069,8.0551,5.5534,6.1287,6.7746</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:18:55</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.508618328999744</v>
+      </c>
+      <c r="F79" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="G79" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="H79" t="n">
+        <v>78</v>
+      </c>
+      <c r="I79" t="n">
+        <v>59.9527</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0:59.95</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>58.504</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.2897</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4676.8796</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1:17:56.88</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0,4,3,7,8,1,9,6,5,2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0:15;4:13;3:21;7:20;8:30;1:23;9:17;6:32;5:35;2:19</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0:[];4:[];3:[4,7];7:[4,6];8:[0,4,6];1:[3];9:[4];6:[4,5,6];5:[2,4,6];2:[3]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>c0:bw=15,experts=[]; c4:bw=13,experts=[]; c3:bw=21,experts=[4,7]; c7:bw=20,experts=[4,6]; c8:bw=30,experts=[0,4,6]; c1:bw=23,experts=[3]; c9:bw=17,experts=[4]; c6:bw=32,experts=[4,5,6]; c5:bw=35,experts=[2,4,6]; c2:bw=19,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>4.9795,7.3707,5.9475,5.3346,6.2566,5.0331,4.0337,7.8274,7.2120,4.5087</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:19:56</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.501954522828091</v>
+      </c>
+      <c r="F80" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="G80" t="n">
+        <v>61.71</v>
+      </c>
+      <c r="H80" t="n">
+        <v>78</v>
+      </c>
+      <c r="I80" t="n">
+        <v>60.9395</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1:00.94</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>59.4846</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.2878</v>
+      </c>
+      <c r="N80" t="n">
+        <v>4738.0636</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1:18:58.06</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>6,9,0,4,7,8,5,3,1,2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>6:12;9:10;0:20;4:40;7:25;8:25;5:29;3:15;1:21;2:18</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>6:[0];9:[2];0:[0,4];4:[0,2,4,6];7:[4,6];8:[2,4];5:[0,4];3:[2];1:[4,6];2:[6]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>c6:bw=12,experts=[0]; c9:bw=10,experts=[2]; c0:bw=20,experts=[0,4]; c4:bw=40,experts=[0,2,4,6]; c7:bw=25,experts=[4,6]; c8:bw=25,experts=[2,4]; c5:bw=29,experts=[0,4]; c3:bw=15,experts=[2]; c1:bw=21,experts=[4,6]; c2:bw=18,experts=[6]</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>7.8293,4.1191,5.3988,7.9286,5.3863,6.1684,7.2269,5.9044,5.0442,4.4785</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:20:58</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.505462187452</v>
+      </c>
+      <c r="F81" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G81" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H81" t="n">
+        <v>80</v>
+      </c>
+      <c r="I81" t="n">
+        <v>61.0481</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1:01.05</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>59.5836</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.2877</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4799.1453</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1:19:59.15</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5,9,7,1,3,4,2,0,6,8</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>5:36;9:29;7:26;1:17;3:17;4:32;2:24;0:26;6:22;8:28</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>5:[4,5,6];9:[0,7];7:[0,7];1:[4];3:[6];4:[4,5];2:[4,6];0:[4,6];6:[4];8:[4]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>c5:bw=36,experts=[4,5,6]; c9:bw=29,experts=[0,7]; c7:bw=26,experts=[0,7]; c1:bw=17,experts=[4]; c3:bw=17,experts=[6]; c4:bw=32,experts=[4,5]; c2:bw=24,experts=[4,6]; c0:bw=26,experts=[4,6]; c6:bw=22,experts=[4]; c8:bw=28,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>7.3336,4.1200,5.4065,5.0304,6.0631,7.8616,4.3782,5.4141,7.7667,6.2094</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:21:59</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.493778683262615</v>
+      </c>
+      <c r="F82" t="n">
+        <v>62.07</v>
+      </c>
+      <c r="G82" t="n">
+        <v>62.07</v>
+      </c>
+      <c r="H82" t="n">
+        <v>81</v>
+      </c>
+      <c r="I82" t="n">
+        <v>61.3359</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1:01.34</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>59.8771</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.2828</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4860.5193</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1:21:00.52</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>6,2,3,1,4,5,9,7,8,0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6:29;2:25;3:37;1:27;4:23;5:17;9:15;7:32;8:26;0:28</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>6:[4,6];2:[0];3:[1,4];1:[0,7];4:[1,4];5:[];9:[];7:[3,4,6];8:[4];0:[1,4]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>c6:bw=29,experts=[4,6]; c2:bw=25,experts=[0]; c3:bw=37,experts=[1,4]; c1:bw=27,experts=[0,7]; c4:bw=23,experts=[1,4]; c5:bw=17,experts=[]; c9:bw=15,experts=[]; c7:bw=32,experts=[3,4,6]; c8:bw=26,experts=[4]; c0:bw=28,experts=[1,4]</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>7.8349,4.4338,6.0323,5.2725,8.1183,7.2965,4.0852,5.2926,6.1711,5.3399</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:23:00</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.48335262812336</v>
+      </c>
+      <c r="F83" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="G83" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="H83" t="n">
+        <v>82</v>
+      </c>
+      <c r="I83" t="n">
+        <v>61.1819</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1:01.18</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>59.7223</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1612</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.2971</v>
+      </c>
+      <c r="N83" t="n">
+        <v>4921.7403</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1:22:01.74</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1,0,6,8,7,3,2,9,5,4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1:36;0:17;6:20;8:32;7:22;3:22;2:16;9:31;5:22;4:16</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1:[1,4];0:[3];6:[1,4];8:[1,4,6];7:[2,4];3:[3];2:[7];9:[0,4,6];5:[1,3];4:[3]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>c1:bw=36,experts=[1,4]; c0:bw=17,experts=[3]; c6:bw=20,experts=[1,4]; c8:bw=32,experts=[1,4,6]; c7:bw=22,experts=[2,4]; c3:bw=22,experts=[3]; c2:bw=16,experts=[7]; c9:bw=31,experts=[0,4,6]; c5:bw=22,experts=[1,3]; c4:bw=16,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>5.1514,5.4118,7.7499,6.3124,5.4523,6.0135,4.3588,4.0934,7.2665,7.9124</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:24:01</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.482419942366244</v>
+      </c>
+      <c r="F84" t="n">
+        <v>62.15</v>
+      </c>
+      <c r="G84" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="H84" t="n">
+        <v>82</v>
+      </c>
+      <c r="I84" t="n">
+        <v>60.7605</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1:00.76</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>59.2786</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.3093</v>
+      </c>
+      <c r="N84" t="n">
+        <v>4982.5341</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:23:02.53</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:29;4:10;2:23;7:21;5:10;0:10;6:29;1:35;8:22;3:24</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[1,4];4:[4];2:[1,2];7:[1,4];5:[4];0:[];6:[2,4];1:[2,4];8:[3,7];3:[0,4]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=29,experts=[1,4]; c4:bw=10,experts=[4]; c2:bw=23,experts=[1,2]; c7:bw=21,experts=[1,4]; c5:bw=10,experts=[4]; c0:bw=10,experts=[]; c6:bw=29,experts=[2,4]; c1:bw=35,experts=[2,4]; c8:bw=22,experts=[3,7]; c3:bw=24,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>4.1127,7.7996,4.3135,5.4664,7.2226,5.3439,7.8072,5.0220,6.2542,5.9365</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:25:02</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.475905084815453</v>
+      </c>
+      <c r="F85" t="n">
+        <v>61.93</v>
+      </c>
+      <c r="G85" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="H85" t="n">
+        <v>82</v>
+      </c>
+      <c r="I85" t="n">
+        <v>60.7133</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1:00.71</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>58.8683</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.6242</v>
+      </c>
+      <c r="N85" t="n">
+        <v>5043.2855</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:24:03.29</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:37;3:18;1:32;6:10;9:11;2:20;7:26;5:11;4:15;0:10</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[4,5,6];3:[4];1:[4,6];6:[];9:[5];2:[4];7:[4,5];5:[4];4:[7];0:[2]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=37,experts=[4,5,6]; c3:bw=18,experts=[4]; c1:bw=32,experts=[4,6]; c6:bw=10,experts=[]; c9:bw=11,experts=[5]; c2:bw=20,experts=[4]; c7:bw=26,experts=[4,5]; c5:bw=11,experts=[4]; c4:bw=15,experts=[7]; c0:bw=10,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>6.2027,5.8811,5.0639,7.8909,4.1021,4.4071,5.3227,7.2001,7.6799,5.1178</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:26:02</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.47094316274407</v>
+      </c>
+      <c r="F86" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="G86" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="H86" t="n">
+        <v>82</v>
+      </c>
+      <c r="I86" t="n">
+        <v>60.3201</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1:00.32</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>58.8483</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.2893</v>
+      </c>
+      <c r="N86" t="n">
+        <v>5103.6516</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:25:03.65</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:21;2:25;8:39;6:23;1:31;4:23;9:32;3:28;5:10;7:10</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[5,7];2:[4,5];8:[4,5,6];6:[3,7];1:[4,5];4:[4,6];9:[3,4,6];3:[4,5];5:[];7:[]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=21,experts=[5,7]; c2:bw=25,experts=[4,5]; c8:bw=39,experts=[4,5,6]; c6:bw=23,experts=[3,7]; c1:bw=31,experts=[4,5]; c4:bw=23,experts=[4,6]; c9:bw=32,experts=[3,4,6]; c3:bw=28,experts=[4,5]; c5:bw=10,experts=[]; c7:bw=10,experts=[]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>5.6540,4.5843,6.3352,8.1659,5.3527,7.3289,3.8843,5.5225,6.7655,5.2551</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:27:03</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.454457726125649</v>
+      </c>
+      <c r="F87" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="G87" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="H87" t="n">
+        <v>86</v>
+      </c>
+      <c r="I87" t="n">
+        <v>60.9782</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>1:00.98</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>59.5292</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.2774</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5164.6636</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:26:04.66</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:26;8:15;2:13;6:31;0:17;4:10;7:24;3:15;1:40;9:24</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[7];8:[0];2:[3];6:[4,5];0:[4];4:[4];7:[4];3:[7];1:[3,4,6];9:[4,6]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=26,experts=[7]; c8:bw=15,experts=[0]; c2:bw=13,experts=[3]; c6:bw=31,experts=[4,5]; c0:bw=17,experts=[4]; c4:bw=10,experts=[4]; c7:bw=24,experts=[4]; c3:bw=15,experts=[7]; c1:bw=40,experts=[3,4,6]; c9:bw=24,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>7.2778,6.1128,4.3847,7.9725,5.3877,7.7865,5.4355,6.0486,5.0370,4.0861</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:28:04</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.470511889102341</v>
+      </c>
+      <c r="F88" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="G88" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="H88" t="n">
+        <v>86</v>
+      </c>
+      <c r="I88" t="n">
+        <v>60.4752</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1:00.48</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>59.0415</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.2595</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5225.1729</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:27:05.17</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:16;2:37;7:12;5:10;6:33;3:38;4:19;9:21;8:26;0:19</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[];2:[4,5,6];7:[4];5:[2];6:[0,4];3:[2,4,6];4:[];9:[2];8:[2];0:[0]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=16,experts=[]; c2:bw=37,experts=[4,5,6]; c7:bw=12,experts=[4]; c5:bw=10,experts=[2]; c6:bw=33,experts=[0,4]; c3:bw=38,experts=[2,4,6]; c4:bw=19,experts=[]; c9:bw=21,experts=[2]; c8:bw=26,experts=[2]; c0:bw=19,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>5.0035,4.3653,5.3278,7.2746,7.7863,5.9666,7.7871,4.0318,6.1790,5.3193</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:29:04</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.465554644759001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="H89" t="n">
+        <v>86</v>
+      </c>
+      <c r="I89" t="n">
+        <v>60.8459</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1:00.85</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>59.3573</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.3338</v>
+      </c>
+      <c r="N89" t="n">
+        <v>5286.053</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:28:06.05</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:24;6:15;3:18;7:23;0:34;4:21;9:17;1:16;5:17;2:25</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[4,6];6:[4];3:[4];7:[0,7];0:[4,6];4:[0,2];9:[7];1:[4];5:[0];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=24,experts=[4,6]; c6:bw=15,experts=[4]; c3:bw=18,experts=[4]; c7:bw=23,experts=[0,7]; c0:bw=34,experts=[4,6]; c4:bw=21,experts=[0,2]; c9:bw=17,experts=[7]; c1:bw=16,experts=[4]; c5:bw=17,experts=[0]; c2:bw=25,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>6.1311,7.7332,6.0473,5.3377,5.4190,7.9053,4.0844,5.1101,7.2367,4.3525</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:30:05</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.462314999125409</v>
+      </c>
+      <c r="F90" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="G90" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="H90" t="n">
+        <v>86</v>
+      </c>
+      <c r="I90" t="n">
+        <v>60.9283</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1:00.93</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>59.4472</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.3242</v>
+      </c>
+      <c r="N90" t="n">
+        <v>5347.0167</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1:29:07.02</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:17;8:40;2:25;9:34;7:12;5:25;0:10;6:18;4:17;1:23</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[];8:[0,4,5,6];2:[0,4];9:[4,5,6];7:[];5:[5,6];0:[1];6:[6];4:[];1:[0,7]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=17,experts=[]; c8:bw=40,experts=[0,4,5,6]; c2:bw=25,experts=[0,4]; c9:bw=34,experts=[4,5,6]; c7:bw=12,experts=[]; c5:bw=25,experts=[5,6]; c0:bw=10,experts=[1]; c6:bw=18,experts=[6]; c4:bw=17,experts=[]; c1:bw=23,experts=[0,7]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>5.9595,6.1647,4.4011,4.1897,5.3326,7.2504,5.3860,7.8576,7.8556,5.0500</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:31:07</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.463326821486155</v>
+      </c>
+      <c r="F91" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="G91" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="H91" t="n">
+        <v>86</v>
+      </c>
+      <c r="I91" t="n">
+        <v>61.7091</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1:01.71</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>60.2499</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.1752</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.2828</v>
+      </c>
+      <c r="N91" t="n">
+        <v>5408.7599</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1:30:08.76</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:40;1:17;3:20;9:35;0:35;6:14;2:12;5:15;8:28;4:20</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[2,3,4,6];1:[1];3:[1,3];9:[0,4];0:[3,4,6];6:[1];2:[7];5:[];8:[1,4];4:[5]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=40,experts=[2,3,4,6]; c1:bw=17,experts=[1]; c3:bw=20,experts=[1,3]; c9:bw=35,experts=[0,4]; c0:bw=35,experts=[3,4,6]; c6:bw=14,experts=[1]; c2:bw=12,experts=[7]; c5:bw=15,experts=[]; c8:bw=28,experts=[1,4]; c4:bw=20,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>5.5785,5.0818,6.1574,4.1446,5.4701,7.8220,4.3930,7.6134,6.1410,7.8479</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:32:09</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.468414541043997</v>
+      </c>
+      <c r="F92" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="G92" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="H92" t="n">
+        <v>86</v>
+      </c>
+      <c r="I92" t="n">
+        <v>61.3195</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1:01.32</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>59.8374</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.3332</v>
+      </c>
+      <c r="N92" t="n">
+        <v>5470.1224</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1:31:10.12</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:28;9:19;5:29;7:29;3:22;4:30;0:12;6:16;2:10;8:13</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[2];9:[1];5:[1];7:[1,4];3:[0,4];4:[1,3,4];0:[];6:[];2:[1];8:[3]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=28,experts=[2]; c9:bw=19,experts=[1]; c5:bw=29,experts=[1]; c7:bw=29,experts=[1,4]; c3:bw=22,experts=[0,4]; c4:bw=30,experts=[1,3,4]; c0:bw=12,experts=[]; c6:bw=16,experts=[]; c2:bw=10,experts=[1]; c8:bw=13,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>5.0635,4.1082,7.4034,5.3900,6.0406,7.9495,5.4362,7.9294,4.3290,6.1876</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:33:10</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.459037873811991</v>
+      </c>
+      <c r="F93" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G93" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="H93" t="n">
+        <v>86</v>
+      </c>
+      <c r="I93" t="n">
+        <v>61.4976</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>1:01.50</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>59.9811</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.3407</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5531.6546</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1:32:11.65</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:16;7:19;1:11;0:16;8:11;6:25;9:31;2:14;5:37;4:15</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[];7:[];1:[];0:[2];8:[7];6:[2,4];9:[4,5,6];2:[2];5:[3,4,6];4:[]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=16,experts=[]; c7:bw=19,experts=[]; c1:bw=11,experts=[]; c0:bw=16,experts=[2]; c8:bw=11,experts=[7]; c6:bw=25,experts=[2,4]; c9:bw=31,experts=[4,5,6]; c2:bw=14,experts=[2]; c5:bw=37,experts=[3,4,6]; c4:bw=15,experts=[]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>6.0412,5.4495,5.0796,5.4800,6.1736,7.8843,3.9536,4.1011,7.6107,8.2075</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:34:10</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.450293693706945</v>
+      </c>
+      <c r="F94" t="n">
+        <v>62.65</v>
+      </c>
+      <c r="G94" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="H94" t="n">
+        <v>86</v>
+      </c>
+      <c r="I94" t="n">
+        <v>59.9897</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0:59.99</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>58.4828</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.3298</v>
+      </c>
+      <c r="N94" t="n">
+        <v>5591.6828</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1:33:11.68</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:26;3:17;7:12;9:32;6:12;8:10;5:10;4:18;0:10;2:28</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[4,5];3:[5];7:[];9:[3,4,6];6:[3];8:[4];5:[4];4:[7];0:[];2:[4,6]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=26,experts=[4,5]; c3:bw=17,experts=[5]; c7:bw=12,experts=[]; c9:bw=32,experts=[3,4,6]; c6:bw=12,experts=[3]; c8:bw=10,experts=[4]; c5:bw=10,experts=[4]; c4:bw=18,experts=[7]; c0:bw=10,experts=[]; c2:bw=28,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>5.3591,6.4369,5.7258,3.7651,7.3151,5.6692,6.7509,7.7412,5.3525,4.3668</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:35:11</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.422584338756086</v>
+      </c>
+      <c r="F95" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="G95" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="H95" t="n">
+        <v>94</v>
+      </c>
+      <c r="I95" t="n">
+        <v>60.9985</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1:01.00</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>59.5417</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.2842</v>
+      </c>
+      <c r="N95" t="n">
+        <v>5652.7249</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1:34:12.72</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:25;2:36;5:23;4:17;6:17;9:28;1:39;8:10;0:31;3:19</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[4,5];2:[3,4,6];5:[4,7];4:[];6:[];9:[4];1:[3,4,6];8:[4];0:[4,5,7];3:[7]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=25,experts=[4,5]; c2:bw=36,experts=[3,4,6]; c5:bw=23,experts=[4,7]; c4:bw=17,experts=[]; c6:bw=17,experts=[]; c9:bw=28,experts=[4]; c1:bw=39,experts=[3,4,6]; c8:bw=10,experts=[4]; c0:bw=31,experts=[4,5,7]; c3:bw=19,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>5.4137,4.4013,7.4190,7.8413,7.7510,4.0646,5.1472,6.1256,5.4360,5.9417</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:36:13</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.431219657338542</v>
+      </c>
+      <c r="F96" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="G96" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="H96" t="n">
+        <v>94</v>
+      </c>
+      <c r="I96" t="n">
+        <v>61.3957</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1:01.40</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>59.8973</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5714.1652</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1:35:14.17</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:33;9:23;4:10;6:22;0:19;3:23;1:17;8:40;2:13;5:10</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[0,4,6];9:[2,4];4:[];6:[5,7];0:[0];3:[2,6];1:[4];8:[2,4,6];2:[5];5:[2]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=33,experts=[0,4,6]; c9:bw=23,experts=[2,4]; c4:bw=10,experts=[]; c6:bw=22,experts=[5,7]; c0:bw=19,experts=[0]; c3:bw=23,experts=[2,6]; c1:bw=17,experts=[4]; c8:bw=40,experts=[2,4,6]; c2:bw=13,experts=[5]; c5:bw=10,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>5.3835,4.1140,8.0286,7.9111,5.4332,5.9453,5.1706,6.2145,4.4124,7.2840</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:37:14</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.416600071685605</v>
+      </c>
+      <c r="F97" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="G97" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="H97" t="n">
+        <v>96</v>
+      </c>
+      <c r="I97" t="n">
+        <v>61.2976</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1:01.30</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>59.8045</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.3043</v>
+      </c>
+      <c r="N97" t="n">
+        <v>5775.501</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1:36:15.50</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:36;9:25;3:25;1:20;5:33;4:27;6:17;7:28;0:20;8:36</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[4,5,6];9:[4,7];3:[4,6];1:[4,6];5:[0,4,6];4:[0,6];6:[0];7:[4,7];0:[4,6];8:[0,4,6]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=36,experts=[4,5,6]; c9:bw=25,experts=[4,7]; c3:bw=25,experts=[4,6]; c1:bw=20,experts=[4,6]; c5:bw=33,experts=[0,4,6]; c4:bw=27,experts=[0,6]; c6:bw=17,experts=[0]; c7:bw=28,experts=[4,7]; c0:bw=20,experts=[4,6]; c8:bw=36,experts=[0,4,6]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>4.4299,4.2002,6.0460,5.0358,7.3023,7.9113,7.9430,5.3614,5.4566,6.1179</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:38:15</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.426627725807296</v>
+      </c>
+      <c r="F98" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="G98" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="H98" t="n">
+        <v>96</v>
+      </c>
+      <c r="I98" t="n">
+        <v>60.9741</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1:00.97</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>59.5226</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.2963</v>
+      </c>
+      <c r="N98" t="n">
+        <v>5836.5177</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1:37:16.52</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:23;9:24;8:24;4:10;7:17;1:28;3:19;5:26;6:28;2:30</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[1];9:[4,6];8:[4,5];4:[];7:[];1:[0];3:[];5:[4,5];6:[6];2:[0,4]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=23,experts=[1]; c9:bw=24,experts=[4,6]; c8:bw=24,experts=[4,5]; c4:bw=10,experts=[]; c7:bw=17,experts=[]; c1:bw=28,experts=[0]; c3:bw=19,experts=[]; c5:bw=26,experts=[4,5]; c6:bw=28,experts=[6]; c2:bw=30,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>5.4558,4.2398,6.1935,7.8594,5.3733,5.0311,6.0701,7.2411,7.7242,4.3343</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:39:16</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.446244163470386</v>
+      </c>
+      <c r="F99" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="G99" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="H99" t="n">
+        <v>96</v>
+      </c>
+      <c r="I99" t="n">
+        <v>61.0594</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1:01.06</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>59.5905</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="N99" t="n">
+        <v>5897.6137</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1:38:17.61</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:29;8:30;9:15;7:13;6:20;5:27;0:19;3:14;1:15;2:13</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[2];8:[1,4,6];9:[0];7:[2];6:[1];5:[4,6];0:[3];3:[1];1:[7];2:[]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=29,experts=[2]; c8:bw=30,experts=[1,4,6]; c9:bw=15,experts=[0]; c7:bw=13,experts=[2]; c6:bw=20,experts=[1]; c5:bw=27,experts=[4,6]; c0:bw=19,experts=[3]; c3:bw=14,experts=[1]; c1:bw=15,experts=[7]; c2:bw=13,experts=[]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>7.9503,6.1303,4.0953,5.3353,7.9534,7.5155,5.3491,5.9207,4.9939,4.3467</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:40:18</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.446973453793114</v>
+      </c>
+      <c r="F100" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="G100" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="H100" t="n">
+        <v>96</v>
+      </c>
+      <c r="I100" t="n">
+        <v>61.4757</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1:01.48</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>59.9822</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.3303</v>
+      </c>
+      <c r="N100" t="n">
+        <v>5959.1273</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1:39:19.13</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:19;5:27;7:25;1:33;3:21;9:11;4:14;0:22;2:17;6:19</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[3];5:[1];7:[1,3];1:[1,2,4];3:[0,3];9:[1];4:[];0:[4,6];2:[7];6:[4]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=19,experts=[3]; c5:bw=27,experts=[1]; c7:bw=25,experts=[1,3]; c1:bw=33,experts=[1,2,4]; c3:bw=21,experts=[0,3]; c9:bw=11,experts=[1]; c4:bw=14,experts=[]; c0:bw=22,experts=[4,6]; c2:bw=17,experts=[7]; c6:bw=19,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>6.4484,7.4966,5.3676,5.0349,5.9668,4.0682,7.9125,5.4228,4.4145,7.8500</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:41:20</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.427833644980662</v>
+      </c>
+      <c r="F101" t="n">
+        <v>63.15</v>
+      </c>
+      <c r="G101" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="H101" t="n">
+        <v>96</v>
+      </c>
+      <c r="I101" t="n">
+        <v>62.7928</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1:02.79</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>61.2276</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.1712</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.3927</v>
+      </c>
+      <c r="N101" t="n">
+        <v>6021.9587</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1:40:21.96</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:17;8:25;9:29;5:10;6:25;1:10;4:36;7:10;3:23;0:36</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[1];8:[7];9:[5];5:[];6:[2,4];1:[4];4:[1,3,5];7:[4];3:[4,6];0:[2,4]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=17,experts=[1]; c8:bw=25,experts=[7]; c9:bw=29,experts=[5]; c5:bw=10,experts=[]; c6:bw=25,experts=[2,4]; c1:bw=10,experts=[4]; c4:bw=36,experts=[1,3,5]; c7:bw=10,experts=[4]; c3:bw=23,experts=[4,6]; c0:bw=36,experts=[2,4]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>4.6959,6.1844,4.1018,7.1814,7.4205,5.1836,8.1444,5.7849,6.5838,5.9469</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
